--- a/212-corriger-interopsanteorg/ig/StructureDefinition-as-practitioner.xlsx
+++ b/212-corriger-interopsanteorg/ig/StructureDefinition-as-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10358" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10358" uniqueCount="916">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T16:13:56+00:00</t>
+    <t>2024-07-01T16:18:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1266,7 +1266,7 @@
   </si>
   <si>
     <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
-Les codes ADELI, RPPS et IDNPS proviennent du system  http://interopsante.org/fhir/CodeSystem/fr-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
+Les codes ADELI, RPPS et IDNPS proviennent du system  https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
   </si>
   <si>
     <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
@@ -1592,10 +1592,6 @@
   </si>
   <si>
     <t>Practitioner.identifier:idNatPs.type</t>
-  </si>
-  <si>
-    <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
-Les codes ADELI, RPPS et IDNPS proviennent du system  https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -18358,7 +18354,7 @@
         <v>243</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>510</v>
+        <v>402</v>
       </c>
       <c r="M116" t="s" s="2">
         <v>403</v>
@@ -18377,7 +18373,7 @@
         <v>83</v>
       </c>
       <c r="S116" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="T116" t="s" s="2">
         <v>83</v>
@@ -18395,10 +18391,10 @@
         <v>167</v>
       </c>
       <c r="Y116" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="Z116" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>83</v>
@@ -18463,7 +18459,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>467</v>
@@ -18495,7 +18491,7 @@
         <v>468</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>470</v>
@@ -18511,7 +18507,7 @@
         <v>83</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>472</v>
@@ -18597,7 +18593,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>477</v>
@@ -18626,7 +18622,7 @@
         <v>114</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="M118" t="s" s="2">
         <v>479</v>
@@ -18729,7 +18725,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>486</v>
@@ -18859,7 +18855,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>493</v>
@@ -18991,13 +18987,13 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>379</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>83</v>
@@ -19022,7 +19018,7 @@
         <v>380</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="M121" t="s" s="2">
         <v>382</v>
@@ -19125,7 +19121,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>390</v>
@@ -19255,7 +19251,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>391</v>
@@ -19387,7 +19383,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>392</v>
@@ -19521,7 +19517,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>401</v>
@@ -19550,7 +19546,7 @@
         <v>243</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="M125" t="s" s="2">
         <v>403</v>
@@ -19569,7 +19565,7 @@
         <v>83</v>
       </c>
       <c r="S125" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="T125" t="s" s="2">
         <v>83</v>
@@ -19587,10 +19583,10 @@
         <v>167</v>
       </c>
       <c r="Y125" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="Z125" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>83</v>
@@ -19655,7 +19651,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>467</v>
@@ -19687,7 +19683,7 @@
         <v>468</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>470</v>
@@ -19703,7 +19699,7 @@
         <v>83</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>472</v>
@@ -19789,7 +19785,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>477</v>
@@ -19921,7 +19917,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>486</v>
@@ -20051,7 +20047,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>493</v>
@@ -20183,13 +20179,13 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>379</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>83</v>
@@ -20214,7 +20210,7 @@
         <v>380</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="M130" t="s" s="2">
         <v>382</v>
@@ -20317,7 +20313,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>390</v>
@@ -20447,7 +20443,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>391</v>
@@ -20579,7 +20575,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>392</v>
@@ -20713,7 +20709,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>401</v>
@@ -20742,7 +20738,7 @@
         <v>243</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="M134" t="s" s="2">
         <v>403</v>
@@ -20761,7 +20757,7 @@
         <v>83</v>
       </c>
       <c r="S134" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="T134" t="s" s="2">
         <v>83</v>
@@ -20779,10 +20775,10 @@
         <v>167</v>
       </c>
       <c r="Y134" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="Z134" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>83</v>
@@ -20847,7 +20843,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>467</v>
@@ -20879,7 +20875,7 @@
         <v>468</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="N135" t="s" s="2">
         <v>470</v>
@@ -20895,7 +20891,7 @@
         <v>83</v>
       </c>
       <c r="S135" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="T135" t="s" s="2">
         <v>472</v>
@@ -20981,7 +20977,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>477</v>
@@ -21113,7 +21109,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>486</v>
@@ -21243,7 +21239,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>493</v>
@@ -21375,10 +21371,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -21404,23 +21400,23 @@
         <v>311</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="M139" t="s" s="2">
+      <c r="N139" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="N139" t="s" s="2">
+      <c r="O139" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="O139" t="s" s="2">
+      <c r="P139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q139" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="P139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q139" t="s" s="2">
-        <v>553</v>
-      </c>
       <c r="R139" t="s" s="2">
         <v>83</v>
       </c>
@@ -21464,7 +21460,7 @@
         <v>83</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>84</v>
@@ -21500,21 +21496,21 @@
         <v>83</v>
       </c>
       <c r="AR139" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AS139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT139" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="AS139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT139" t="s" s="2">
-        <v>555</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -21537,19 +21533,19 @@
         <v>83</v>
       </c>
       <c r="K140" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="L140" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="L140" t="s" s="2">
+      <c r="M140" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="M140" t="s" s="2">
+      <c r="N140" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="N140" t="s" s="2">
+      <c r="O140" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>83</v>
@@ -21598,7 +21594,7 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>84</v>
@@ -21631,13 +21627,13 @@
         <v>83</v>
       </c>
       <c r="AQ140" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AR140" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="AR140" t="s" s="2">
+      <c r="AS140" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="AS140" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="AT140" t="s" s="2">
         <v>83</v>
@@ -21645,10 +21641,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -21775,10 +21771,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -21907,13 +21903,13 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="C143" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="B143" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="C143" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="D143" t="s" s="2">
         <v>83</v>
@@ -21935,13 +21931,13 @@
         <v>83</v>
       </c>
       <c r="K143" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="L143" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="L143" t="s" s="2">
+      <c r="M143" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -22039,10 +22035,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -22068,16 +22064,16 @@
         <v>185</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="M144" t="s" s="2">
+      <c r="N144" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="N144" t="s" s="2">
+      <c r="O144" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="O144" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>83</v>
@@ -22106,25 +22102,25 @@
       </c>
       <c r="Y144" s="2"/>
       <c r="Z144" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AA144" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB144" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD144" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE144" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF144" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="AA144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF144" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>84</v>
@@ -22157,13 +22153,13 @@
         <v>83</v>
       </c>
       <c r="AQ144" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AR144" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="AR144" t="s" s="2">
+      <c r="AS144" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="AS144" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="AT144" t="s" s="2">
         <v>83</v>
@@ -22171,10 +22167,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -22200,16 +22196,16 @@
         <v>114</v>
       </c>
       <c r="L145" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M145" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="M145" t="s" s="2">
+      <c r="N145" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="N145" t="s" s="2">
+      <c r="O145" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="O145" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>83</v>
@@ -22258,7 +22254,7 @@
         <v>83</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>84</v>
@@ -22291,10 +22287,10 @@
         <v>83</v>
       </c>
       <c r="AQ145" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AR145" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="AR145" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="AS145" t="s" s="2">
         <v>83</v>
@@ -22305,14 +22301,14 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
@@ -22334,13 +22330,13 @@
         <v>114</v>
       </c>
       <c r="L146" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M146" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="M146" t="s" s="2">
+      <c r="N146" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="N146" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -22390,7 +22386,7 @@
         <v>83</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>84</v>
@@ -22408,28 +22404,28 @@
         <v>83</v>
       </c>
       <c r="AL146" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AM146" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN146" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO146" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP146" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ146" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="AM146" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN146" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO146" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP146" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ146" t="s" s="2">
+      <c r="AR146" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="AR146" t="s" s="2">
+      <c r="AS146" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="AS146" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="AT146" t="s" s="2">
         <v>83</v>
@@ -22437,14 +22433,14 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
@@ -22466,13 +22462,13 @@
         <v>114</v>
       </c>
       <c r="L147" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M147" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="M147" t="s" s="2">
+      <c r="N147" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -22522,7 +22518,7 @@
         <v>83</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>84</v>
@@ -22540,28 +22536,28 @@
         <v>83</v>
       </c>
       <c r="AL147" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AM147" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN147" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO147" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP147" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ147" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="AM147" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN147" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO147" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP147" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ147" t="s" s="2">
+      <c r="AR147" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="AR147" t="s" s="2">
+      <c r="AS147" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="AS147" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="AT147" t="s" s="2">
         <v>83</v>
@@ -22569,10 +22565,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -22598,10 +22594,10 @@
         <v>114</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M148" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -22631,28 +22627,28 @@
         <v>167</v>
       </c>
       <c r="Y148" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="Z148" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="Z148" t="s" s="2">
+      <c r="AA148" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF148" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="AA148" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB148" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC148" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD148" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE148" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF148" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>84</v>
@@ -22685,13 +22681,13 @@
         <v>83</v>
       </c>
       <c r="AQ148" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AR148" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="AR148" t="s" s="2">
+      <c r="AS148" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="AS148" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="AT148" t="s" s="2">
         <v>83</v>
@@ -22699,10 +22695,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -22728,10 +22724,10 @@
         <v>114</v>
       </c>
       <c r="L149" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M149" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -22761,28 +22757,28 @@
         <v>167</v>
       </c>
       <c r="Y149" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="Z149" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="Z149" t="s" s="2">
+      <c r="AA149" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB149" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC149" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD149" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE149" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF149" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="AA149" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB149" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC149" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD149" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE149" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF149" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>84</v>
@@ -22800,25 +22796,25 @@
         <v>83</v>
       </c>
       <c r="AL149" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AM149" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN149" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO149" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP149" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ149" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="AM149" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN149" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO149" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP149" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ149" t="s" s="2">
+      <c r="AR149" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="AR149" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="AS149" t="s" s="2">
         <v>83</v>
@@ -22829,10 +22825,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -22858,14 +22854,14 @@
         <v>263</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="M150" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>83</v>
@@ -22914,7 +22910,7 @@
         <v>83</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>84</v>
@@ -22947,10 +22943,10 @@
         <v>83</v>
       </c>
       <c r="AQ150" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AR150" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="AR150" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="AS150" t="s" s="2">
         <v>492</v>
@@ -22961,10 +22957,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -22987,19 +22983,19 @@
         <v>83</v>
       </c>
       <c r="K151" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="L151" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="L151" t="s" s="2">
+      <c r="M151" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="M151" t="s" s="2">
+      <c r="N151" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="N151" t="s" s="2">
+      <c r="O151" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="O151" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>83</v>
@@ -23036,7 +23032,7 @@
         <v>83</v>
       </c>
       <c r="AB151" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AC151" s="2"/>
       <c r="AD151" t="s" s="2">
@@ -23046,7 +23042,7 @@
         <v>127</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>84</v>
@@ -23058,34 +23054,34 @@
         <v>218</v>
       </c>
       <c r="AJ151" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AK151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO151" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="AK151" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL151" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM151" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN151" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO151" t="s" s="2">
+      <c r="AP151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ151" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="AP151" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ151" t="s" s="2">
+      <c r="AR151" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="AR151" t="s" s="2">
+      <c r="AS151" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="AS151" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="AT151" t="s" s="2">
         <v>83</v>
@@ -23093,10 +23089,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -23223,10 +23219,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -23355,13 +23351,13 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="C154" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="B154" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="C154" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="D154" t="s" s="2">
         <v>83</v>
@@ -23383,13 +23379,13 @@
         <v>83</v>
       </c>
       <c r="K154" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="L154" t="s" s="2">
         <v>651</v>
       </c>
-      <c r="L154" t="s" s="2">
+      <c r="M154" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -23487,10 +23483,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -23516,10 +23512,10 @@
         <v>185</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="M155" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -23549,28 +23545,28 @@
         <v>246</v>
       </c>
       <c r="Y155" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="Z155" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="Z155" t="s" s="2">
+      <c r="AA155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF155" t="s" s="2">
         <v>658</v>
-      </c>
-      <c r="AA155" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB155" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC155" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD155" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE155" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF155" t="s" s="2">
-        <v>659</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>84</v>
@@ -23579,7 +23575,7 @@
         <v>100</v>
       </c>
       <c r="AI155" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AJ155" t="s" s="2">
         <v>112</v>
@@ -23603,13 +23599,13 @@
         <v>83</v>
       </c>
       <c r="AQ155" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="AR155" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="AR155" t="s" s="2">
+      <c r="AS155" t="s" s="2">
         <v>662</v>
-      </c>
-      <c r="AS155" t="s" s="2">
-        <v>663</v>
       </c>
       <c r="AT155" t="s" s="2">
         <v>83</v>
@@ -23617,10 +23613,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -23646,16 +23642,16 @@
         <v>114</v>
       </c>
       <c r="L156" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="M156" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="M156" t="s" s="2">
+      <c r="N156" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="N156" t="s" s="2">
+      <c r="O156" t="s" s="2">
         <v>667</v>
-      </c>
-      <c r="O156" t="s" s="2">
-        <v>668</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>83</v>
@@ -23704,7 +23700,7 @@
         <v>83</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>84</v>
@@ -23737,10 +23733,10 @@
         <v>83</v>
       </c>
       <c r="AQ156" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="AR156" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="AR156" t="s" s="2">
-        <v>671</v>
       </c>
       <c r="AS156" t="s" s="2">
         <v>485</v>
@@ -23751,10 +23747,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -23780,16 +23776,16 @@
         <v>185</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="M157" t="s" s="2">
         <v>673</v>
       </c>
-      <c r="M157" t="s" s="2">
+      <c r="N157" t="s" s="2">
         <v>674</v>
       </c>
-      <c r="N157" t="s" s="2">
+      <c r="O157" t="s" s="2">
         <v>675</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>676</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>83</v>
@@ -23817,28 +23813,28 @@
         <v>246</v>
       </c>
       <c r="Y157" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="Z157" t="s" s="2">
         <v>677</v>
       </c>
-      <c r="Z157" t="s" s="2">
+      <c r="AA157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF157" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="AA157" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB157" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC157" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD157" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE157" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF157" t="s" s="2">
-        <v>679</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>84</v>
@@ -23871,13 +23867,13 @@
         <v>83</v>
       </c>
       <c r="AQ157" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="AR157" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AS157" t="s" s="2">
         <v>680</v>
-      </c>
-      <c r="AR157" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="AS157" t="s" s="2">
-        <v>681</v>
       </c>
       <c r="AT157" t="s" s="2">
         <v>83</v>
@@ -23885,10 +23881,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -23911,16 +23907,16 @@
         <v>101</v>
       </c>
       <c r="K158" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="L158" t="s" s="2">
         <v>683</v>
       </c>
-      <c r="L158" t="s" s="2">
+      <c r="M158" t="s" s="2">
         <v>684</v>
       </c>
-      <c r="M158" t="s" s="2">
+      <c r="N158" t="s" s="2">
         <v>685</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>686</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -23970,7 +23966,7 @@
         <v>83</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>84</v>
@@ -24017,10 +24013,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -24046,10 +24042,10 @@
         <v>263</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="M159" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>690</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -24100,7 +24096,7 @@
         <v>83</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>84</v>
@@ -24136,7 +24132,7 @@
         <v>208</v>
       </c>
       <c r="AR159" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AS159" t="s" s="2">
         <v>492</v>
@@ -24147,13 +24143,13 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="C160" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="B160" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="C160" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="D160" t="s" s="2">
         <v>83</v>
@@ -24175,19 +24171,19 @@
         <v>83</v>
       </c>
       <c r="K160" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="L160" t="s" s="2">
         <v>694</v>
       </c>
-      <c r="L160" t="s" s="2">
-        <v>695</v>
-      </c>
       <c r="M160" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="N160" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="N160" t="s" s="2">
+      <c r="O160" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="O160" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>83</v>
@@ -24236,7 +24232,7 @@
         <v>83</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>84</v>
@@ -24248,13 +24244,13 @@
         <v>218</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>83</v>
@@ -24269,13 +24265,13 @@
         <v>83</v>
       </c>
       <c r="AQ160" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AR160" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="AR160" t="s" s="2">
+      <c r="AS160" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="AS160" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="AT160" t="s" s="2">
         <v>83</v>
@@ -24283,10 +24279,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -24309,19 +24305,19 @@
         <v>83</v>
       </c>
       <c r="K161" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="L161" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="L161" t="s" s="2">
+      <c r="M161" t="s" s="2">
         <v>699</v>
       </c>
-      <c r="M161" t="s" s="2">
+      <c r="N161" t="s" s="2">
         <v>700</v>
       </c>
-      <c r="N161" t="s" s="2">
+      <c r="O161" t="s" s="2">
         <v>701</v>
-      </c>
-      <c r="O161" t="s" s="2">
-        <v>702</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>83</v>
@@ -24370,7 +24366,7 @@
         <v>83</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>84</v>
@@ -24397,19 +24393,19 @@
         <v>83</v>
       </c>
       <c r="AO161" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="AP161" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ161" t="s" s="2">
         <v>703</v>
       </c>
-      <c r="AP161" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ161" t="s" s="2">
+      <c r="AR161" t="s" s="2">
         <v>704</v>
       </c>
-      <c r="AR161" t="s" s="2">
+      <c r="AS161" t="s" s="2">
         <v>705</v>
-      </c>
-      <c r="AS161" t="s" s="2">
-        <v>706</v>
       </c>
       <c r="AT161" t="s" s="2">
         <v>83</v>
@@ -24417,10 +24413,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -24446,14 +24442,14 @@
         <v>185</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="M162" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>83</v>
@@ -24481,11 +24477,11 @@
         <v>246</v>
       </c>
       <c r="Y162" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="Z162" t="s" s="2">
         <v>711</v>
       </c>
-      <c r="Z162" t="s" s="2">
-        <v>712</v>
-      </c>
       <c r="AA162" t="s" s="2">
         <v>83</v>
       </c>
@@ -24502,7 +24498,7 @@
         <v>83</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>84</v>
@@ -24535,13 +24531,13 @@
         <v>83</v>
       </c>
       <c r="AQ162" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="AR162" t="s" s="2">
         <v>713</v>
       </c>
-      <c r="AR162" t="s" s="2">
+      <c r="AS162" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="AS162" t="s" s="2">
-        <v>715</v>
       </c>
       <c r="AT162" t="s" s="2">
         <v>83</v>
@@ -24549,10 +24545,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -24575,17 +24571,17 @@
         <v>101</v>
       </c>
       <c r="K163" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="L163" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="L163" t="s" s="2">
+      <c r="M163" t="s" s="2">
         <v>718</v>
-      </c>
-      <c r="M163" t="s" s="2">
-        <v>719</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>83</v>
@@ -24634,7 +24630,7 @@
         <v>83</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>84</v>
@@ -24667,13 +24663,13 @@
         <v>83</v>
       </c>
       <c r="AQ163" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="AR163" t="s" s="2">
         <v>721</v>
       </c>
-      <c r="AR163" t="s" s="2">
+      <c r="AS163" t="s" s="2">
         <v>722</v>
-      </c>
-      <c r="AS163" t="s" s="2">
-        <v>723</v>
       </c>
       <c r="AT163" t="s" s="2">
         <v>83</v>
@@ -24681,10 +24677,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -24707,17 +24703,17 @@
         <v>83</v>
       </c>
       <c r="K164" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="L164" t="s" s="2">
         <v>725</v>
       </c>
-      <c r="L164" t="s" s="2">
+      <c r="M164" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="M164" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>83</v>
@@ -24766,7 +24762,7 @@
         <v>83</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>84</v>
@@ -24802,10 +24798,10 @@
         <v>83</v>
       </c>
       <c r="AR164" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="AS164" t="s" s="2">
         <v>729</v>
-      </c>
-      <c r="AS164" t="s" s="2">
-        <v>730</v>
       </c>
       <c r="AT164" t="s" s="2">
         <v>83</v>
@@ -24813,10 +24809,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -24839,13 +24835,13 @@
         <v>83</v>
       </c>
       <c r="K165" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="L165" t="s" s="2">
         <v>732</v>
       </c>
-      <c r="L165" t="s" s="2">
+      <c r="M165" t="s" s="2">
         <v>733</v>
-      </c>
-      <c r="M165" t="s" s="2">
-        <v>734</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -24884,7 +24880,7 @@
         <v>83</v>
       </c>
       <c r="AB165" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="AC165" s="2"/>
       <c r="AD165" t="s" s="2">
@@ -24894,7 +24890,7 @@
         <v>127</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>84</v>
@@ -24927,13 +24923,13 @@
         <v>83</v>
       </c>
       <c r="AQ165" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="AR165" t="s" s="2">
         <v>736</v>
       </c>
-      <c r="AR165" t="s" s="2">
+      <c r="AS165" t="s" s="2">
         <v>737</v>
-      </c>
-      <c r="AS165" t="s" s="2">
-        <v>738</v>
       </c>
       <c r="AT165" t="s" s="2">
         <v>83</v>
@@ -24941,10 +24937,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -25071,10 +25067,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -25203,14 +25199,14 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
@@ -25232,10 +25228,10 @@
         <v>121</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="M168" t="s" s="2">
         <v>743</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>744</v>
       </c>
       <c r="N168" t="s" s="2">
         <v>124</v>
@@ -25290,7 +25286,7 @@
         <v>83</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>84</v>
@@ -25337,10 +25333,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -25366,14 +25362,14 @@
         <v>380</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>747</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>748</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>83</v>
@@ -25422,7 +25418,7 @@
         <v>83</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>84</v>
@@ -25446,19 +25442,19 @@
         <v>83</v>
       </c>
       <c r="AN169" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="AO169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR169" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="AO169" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP169" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ169" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR169" t="s" s="2">
-        <v>751</v>
       </c>
       <c r="AS169" t="s" s="2">
         <v>83</v>
@@ -25469,10 +25465,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -25498,10 +25494,10 @@
         <v>243</v>
       </c>
       <c r="L170" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="M170" t="s" s="2">
         <v>753</v>
-      </c>
-      <c r="M170" t="s" s="2">
-        <v>754</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -25532,7 +25528,7 @@
       </c>
       <c r="Y170" s="2"/>
       <c r="Z170" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>83</v>
@@ -25550,7 +25546,7 @@
         <v>83</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>100</v>
@@ -25574,22 +25570,22 @@
         <v>83</v>
       </c>
       <c r="AN170" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="AO170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR170" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="AS170" t="s" s="2">
         <v>756</v>
-      </c>
-      <c r="AO170" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP170" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ170" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR170" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="AS170" t="s" s="2">
-        <v>757</v>
       </c>
       <c r="AT170" t="s" s="2">
         <v>83</v>
@@ -25597,10 +25593,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -25626,14 +25622,14 @@
         <v>263</v>
       </c>
       <c r="L171" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="M171" t="s" s="2">
         <v>759</v>
-      </c>
-      <c r="M171" t="s" s="2">
-        <v>760</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>83</v>
@@ -25682,7 +25678,7 @@
         <v>83</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>84</v>
@@ -25718,10 +25714,10 @@
         <v>83</v>
       </c>
       <c r="AR171" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="AS171" t="s" s="2">
         <v>762</v>
-      </c>
-      <c r="AS171" t="s" s="2">
-        <v>763</v>
       </c>
       <c r="AT171" t="s" s="2">
         <v>83</v>
@@ -25729,10 +25725,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -25758,10 +25754,10 @@
         <v>494</v>
       </c>
       <c r="L172" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="M172" t="s" s="2">
         <v>765</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>766</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -25812,7 +25808,7 @@
         <v>83</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>84</v>
@@ -25848,7 +25844,7 @@
         <v>83</v>
       </c>
       <c r="AR172" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="AS172" t="s" s="2">
         <v>83</v>
@@ -25859,13 +25855,13 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="C173" t="s" s="2">
         <v>768</v>
-      </c>
-      <c r="B173" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="C173" t="s" s="2">
-        <v>769</v>
       </c>
       <c r="D173" t="s" s="2">
         <v>83</v>
@@ -25887,13 +25883,13 @@
         <v>83</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -25944,7 +25940,7 @@
         <v>83</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>84</v>
@@ -25968,7 +25964,7 @@
         <v>83</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="AO173" t="s" s="2">
         <v>83</v>
@@ -25977,13 +25973,13 @@
         <v>83</v>
       </c>
       <c r="AQ173" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="AR173" t="s" s="2">
         <v>736</v>
       </c>
-      <c r="AR173" t="s" s="2">
+      <c r="AS173" t="s" s="2">
         <v>737</v>
-      </c>
-      <c r="AS173" t="s" s="2">
-        <v>738</v>
       </c>
       <c r="AT173" t="s" s="2">
         <v>83</v>
@@ -25991,10 +25987,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -26121,10 +26117,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -26249,13 +26245,13 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="C176" t="s" s="2">
         <v>774</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="C176" t="s" s="2">
-        <v>775</v>
       </c>
       <c r="D176" t="s" s="2">
         <v>83</v>
@@ -26277,13 +26273,13 @@
         <v>83</v>
       </c>
       <c r="K176" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="L176" t="s" s="2">
         <v>776</v>
       </c>
-      <c r="L176" t="s" s="2">
+      <c r="M176" t="s" s="2">
         <v>777</v>
-      </c>
-      <c r="M176" t="s" s="2">
-        <v>778</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -26381,10 +26377,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="B177" t="s" s="2">
         <v>779</v>
-      </c>
-      <c r="B177" t="s" s="2">
-        <v>780</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -26511,10 +26507,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="B178" t="s" s="2">
         <v>781</v>
-      </c>
-      <c r="B178" t="s" s="2">
-        <v>782</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -26643,13 +26639,13 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="B179" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="C179" t="s" s="2">
         <v>783</v>
-      </c>
-      <c r="B179" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="C179" t="s" s="2">
-        <v>784</v>
       </c>
       <c r="D179" t="s" s="2">
         <v>83</v>
@@ -26752,7 +26748,7 @@
         <v>83</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>83</v>
@@ -26775,10 +26771,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="B180" t="s" s="2">
         <v>786</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>787</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -26905,10 +26901,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="B181" t="s" s="2">
         <v>788</v>
-      </c>
-      <c r="B181" t="s" s="2">
-        <v>789</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -27035,10 +27031,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="B182" t="s" s="2">
         <v>790</v>
-      </c>
-      <c r="B182" t="s" s="2">
-        <v>791</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -27078,7 +27074,7 @@
       </c>
       <c r="Q182" s="2"/>
       <c r="R182" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="S182" t="s" s="2">
         <v>83</v>
@@ -27167,10 +27163,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="B183" t="s" s="2">
         <v>792</v>
-      </c>
-      <c r="B183" t="s" s="2">
-        <v>793</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -27230,7 +27226,7 @@
       </c>
       <c r="Y183" s="2"/>
       <c r="Z183" t="s" s="2">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>83</v>
@@ -27295,13 +27291,13 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="B184" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="C184" t="s" s="2">
         <v>795</v>
-      </c>
-      <c r="B184" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="C184" t="s" s="2">
-        <v>796</v>
       </c>
       <c r="D184" t="s" s="2">
         <v>83</v>
@@ -27404,7 +27400,7 @@
         <v>83</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>83</v>
@@ -27427,10 +27423,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -27557,10 +27553,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -27687,10 +27683,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -27730,7 +27726,7 @@
       </c>
       <c r="Q187" s="2"/>
       <c r="R187" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="S187" t="s" s="2">
         <v>83</v>
@@ -27819,10 +27815,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -27882,7 +27878,7 @@
       </c>
       <c r="Y188" s="2"/>
       <c r="Z188" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>83</v>
@@ -27947,13 +27943,13 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="B189" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="C189" t="s" s="2">
         <v>803</v>
-      </c>
-      <c r="B189" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="C189" t="s" s="2">
-        <v>804</v>
       </c>
       <c r="D189" t="s" s="2">
         <v>83</v>
@@ -28056,7 +28052,7 @@
         <v>83</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="AO189" t="s" s="2">
         <v>83</v>
@@ -28079,10 +28075,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -28209,10 +28205,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -28339,10 +28335,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -28382,7 +28378,7 @@
       </c>
       <c r="Q192" s="2"/>
       <c r="R192" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="S192" t="s" s="2">
         <v>83</v>
@@ -28471,10 +28467,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -28534,7 +28530,7 @@
       </c>
       <c r="Y193" s="2"/>
       <c r="Z193" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="AA193" t="s" s="2">
         <v>83</v>
@@ -28599,10 +28595,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="B194" t="s" s="2">
         <v>811</v>
-      </c>
-      <c r="B194" t="s" s="2">
-        <v>812</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -28642,7 +28638,7 @@
       </c>
       <c r="Q194" s="2"/>
       <c r="R194" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="S194" t="s" s="2">
         <v>83</v>
@@ -28731,10 +28727,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="B195" t="s" s="2">
         <v>814</v>
-      </c>
-      <c r="B195" t="s" s="2">
-        <v>815</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -28861,14 +28857,14 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E196" s="2"/>
       <c r="F196" t="s" s="2">
@@ -28890,10 +28886,10 @@
         <v>121</v>
       </c>
       <c r="L196" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="M196" t="s" s="2">
         <v>743</v>
-      </c>
-      <c r="M196" t="s" s="2">
-        <v>744</v>
       </c>
       <c r="N196" t="s" s="2">
         <v>124</v>
@@ -28948,7 +28944,7 @@
         <v>83</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>84</v>
@@ -28995,10 +28991,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -29024,14 +29020,14 @@
         <v>380</v>
       </c>
       <c r="L197" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="M197" t="s" s="2">
         <v>747</v>
-      </c>
-      <c r="M197" t="s" s="2">
-        <v>748</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="P197" t="s" s="2">
         <v>83</v>
@@ -29080,7 +29076,7 @@
         <v>83</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>84</v>
@@ -29116,7 +29112,7 @@
         <v>83</v>
       </c>
       <c r="AR197" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="AS197" t="s" s="2">
         <v>83</v>
@@ -29127,10 +29123,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -29156,10 +29152,10 @@
         <v>243</v>
       </c>
       <c r="L198" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="M198" t="s" s="2">
         <v>753</v>
-      </c>
-      <c r="M198" t="s" s="2">
-        <v>754</v>
       </c>
       <c r="N198" s="2"/>
       <c r="O198" s="2"/>
@@ -29190,7 +29186,7 @@
       </c>
       <c r="Y198" s="2"/>
       <c r="Z198" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>83</v>
@@ -29208,7 +29204,7 @@
         <v>83</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>100</v>
@@ -29244,10 +29240,10 @@
         <v>83</v>
       </c>
       <c r="AR198" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AS198" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AT198" t="s" s="2">
         <v>83</v>
@@ -29255,10 +29251,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="B199" t="s" s="2">
         <v>819</v>
-      </c>
-      <c r="B199" t="s" s="2">
-        <v>820</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -29385,10 +29381,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="B200" t="s" s="2">
         <v>821</v>
-      </c>
-      <c r="B200" t="s" s="2">
-        <v>822</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -29517,10 +29513,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="B201" t="s" s="2">
         <v>823</v>
-      </c>
-      <c r="B201" t="s" s="2">
-        <v>824</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -29592,14 +29588,14 @@
         <v>83</v>
       </c>
       <c r="AB201" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AC201" s="2"/>
       <c r="AD201" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE201" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="AF201" t="s" s="2">
         <v>416</v>
@@ -29649,13 +29645,13 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="B202" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="C202" t="s" s="2">
         <v>827</v>
-      </c>
-      <c r="B202" t="s" s="2">
-        <v>824</v>
-      </c>
-      <c r="C202" t="s" s="2">
-        <v>828</v>
       </c>
       <c r="D202" t="s" s="2">
         <v>83</v>
@@ -29718,7 +29714,7 @@
       </c>
       <c r="Y202" s="2"/>
       <c r="Z202" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>83</v>
@@ -29783,13 +29779,13 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D203" t="s" s="2">
         <v>83</v>
@@ -29852,7 +29848,7 @@
       </c>
       <c r="Y203" s="2"/>
       <c r="Z203" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AA203" t="s" s="2">
         <v>83</v>
@@ -29917,10 +29913,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="B204" t="s" s="2">
         <v>831</v>
-      </c>
-      <c r="B204" t="s" s="2">
-        <v>832</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -30051,10 +30047,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -30080,14 +30076,14 @@
         <v>263</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="P205" t="s" s="2">
         <v>83</v>
@@ -30136,7 +30132,7 @@
         <v>83</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>84</v>
@@ -30172,10 +30168,10 @@
         <v>83</v>
       </c>
       <c r="AR205" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="AS205" t="s" s="2">
         <v>762</v>
-      </c>
-      <c r="AS205" t="s" s="2">
-        <v>763</v>
       </c>
       <c r="AT205" t="s" s="2">
         <v>83</v>
@@ -30183,10 +30179,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
+        <v>834</v>
+      </c>
+      <c r="B206" t="s" s="2">
         <v>835</v>
-      </c>
-      <c r="B206" t="s" s="2">
-        <v>836</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -30313,10 +30309,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="B207" t="s" s="2">
         <v>837</v>
-      </c>
-      <c r="B207" t="s" s="2">
-        <v>838</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -30445,10 +30441,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
+        <v>838</v>
+      </c>
+      <c r="B208" t="s" s="2">
         <v>839</v>
-      </c>
-      <c r="B208" t="s" s="2">
-        <v>840</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -30474,7 +30470,7 @@
         <v>270</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="M208" t="s" s="2">
         <v>272</v>
@@ -30554,7 +30550,7 @@
         <v>83</v>
       </c>
       <c r="AN208" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="AO208" t="s" s="2">
         <v>83</v>
@@ -30577,10 +30573,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
+        <v>842</v>
+      </c>
+      <c r="B209" t="s" s="2">
         <v>843</v>
-      </c>
-      <c r="B209" t="s" s="2">
-        <v>844</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -30606,7 +30602,7 @@
         <v>270</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="M209" t="s" s="2">
         <v>282</v>
@@ -30688,7 +30684,7 @@
         <v>83</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="AO209" t="s" s="2">
         <v>83</v>
@@ -30711,10 +30707,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -30737,13 +30733,13 @@
         <v>83</v>
       </c>
       <c r="K210" t="s" s="2">
+        <v>847</v>
+      </c>
+      <c r="L210" t="s" s="2">
         <v>848</v>
       </c>
-      <c r="L210" t="s" s="2">
-        <v>849</v>
-      </c>
       <c r="M210" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="N210" s="2"/>
       <c r="O210" s="2"/>
@@ -30794,7 +30790,7 @@
         <v>83</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>84</v>
@@ -30818,7 +30814,7 @@
         <v>83</v>
       </c>
       <c r="AN210" t="s" s="2">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AO210" t="s" s="2">
         <v>83</v>
@@ -30830,7 +30826,7 @@
         <v>83</v>
       </c>
       <c r="AR210" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="AS210" t="s" s="2">
         <v>83</v>
@@ -30841,13 +30837,13 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
+        <v>850</v>
+      </c>
+      <c r="B211" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="C211" t="s" s="2">
         <v>851</v>
-      </c>
-      <c r="B211" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="C211" t="s" s="2">
-        <v>852</v>
       </c>
       <c r="D211" t="s" s="2">
         <v>83</v>
@@ -30869,13 +30865,13 @@
         <v>83</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="N211" s="2"/>
       <c r="O211" s="2"/>
@@ -30926,7 +30922,7 @@
         <v>83</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>84</v>
@@ -30959,13 +30955,13 @@
         <v>83</v>
       </c>
       <c r="AQ211" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="AR211" t="s" s="2">
         <v>736</v>
       </c>
-      <c r="AR211" t="s" s="2">
+      <c r="AS211" t="s" s="2">
         <v>737</v>
-      </c>
-      <c r="AS211" t="s" s="2">
-        <v>738</v>
       </c>
       <c r="AT211" t="s" s="2">
         <v>83</v>
@@ -30973,10 +30969,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -31103,10 +31099,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -31235,14 +31231,14 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E214" s="2"/>
       <c r="F214" t="s" s="2">
@@ -31264,10 +31260,10 @@
         <v>121</v>
       </c>
       <c r="L214" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="M214" t="s" s="2">
         <v>743</v>
-      </c>
-      <c r="M214" t="s" s="2">
-        <v>744</v>
       </c>
       <c r="N214" t="s" s="2">
         <v>124</v>
@@ -31322,7 +31318,7 @@
         <v>83</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>84</v>
@@ -31369,10 +31365,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -31398,14 +31394,14 @@
         <v>380</v>
       </c>
       <c r="L215" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="M215" t="s" s="2">
         <v>747</v>
-      </c>
-      <c r="M215" t="s" s="2">
-        <v>748</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>83</v>
@@ -31454,7 +31450,7 @@
         <v>83</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>84</v>
@@ -31490,7 +31486,7 @@
         <v>83</v>
       </c>
       <c r="AR215" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="AS215" t="s" s="2">
         <v>83</v>
@@ -31501,10 +31497,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -31530,10 +31526,10 @@
         <v>243</v>
       </c>
       <c r="L216" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="M216" t="s" s="2">
         <v>753</v>
-      </c>
-      <c r="M216" t="s" s="2">
-        <v>754</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" s="2"/>
@@ -31564,7 +31560,7 @@
       </c>
       <c r="Y216" s="2"/>
       <c r="Z216" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AA216" t="s" s="2">
         <v>83</v>
@@ -31582,7 +31578,7 @@
         <v>83</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>100</v>
@@ -31618,10 +31614,10 @@
         <v>83</v>
       </c>
       <c r="AR216" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AS216" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AT216" t="s" s="2">
         <v>83</v>
@@ -31629,10 +31625,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -31759,10 +31755,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -31891,10 +31887,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -31966,14 +31962,14 @@
         <v>83</v>
       </c>
       <c r="AB219" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AC219" s="2"/>
       <c r="AD219" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE219" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="AF219" t="s" s="2">
         <v>416</v>
@@ -32023,13 +32019,13 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="B220" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="C220" t="s" s="2">
         <v>862</v>
-      </c>
-      <c r="B220" t="s" s="2">
-        <v>824</v>
-      </c>
-      <c r="C220" t="s" s="2">
-        <v>863</v>
       </c>
       <c r="D220" t="s" s="2">
         <v>83</v>
@@ -32054,7 +32050,7 @@
         <v>163</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="M220" t="s" s="2">
         <v>413</v>
@@ -32092,7 +32088,7 @@
       </c>
       <c r="Y220" s="2"/>
       <c r="Z220" t="s" s="2">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="AA220" t="s" s="2">
         <v>83</v>
@@ -32128,7 +32124,7 @@
         <v>83</v>
       </c>
       <c r="AL220" t="s" s="2">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="AM220" t="s" s="2">
         <v>83</v>
@@ -32157,10 +32153,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C221" t="s" s="2">
         <v>355</v>
@@ -32188,7 +32184,7 @@
         <v>163</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="M221" t="s" s="2">
         <v>413</v>
@@ -32291,10 +32287,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -32425,10 +32421,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -32454,14 +32450,14 @@
         <v>263</v>
       </c>
       <c r="L223" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="M223" t="s" s="2">
         <v>759</v>
-      </c>
-      <c r="M223" t="s" s="2">
-        <v>760</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="P223" t="s" s="2">
         <v>83</v>
@@ -32510,7 +32506,7 @@
         <v>83</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>84</v>
@@ -32546,10 +32542,10 @@
         <v>83</v>
       </c>
       <c r="AR223" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="AS223" t="s" s="2">
         <v>762</v>
-      </c>
-      <c r="AS223" t="s" s="2">
-        <v>763</v>
       </c>
       <c r="AT223" t="s" s="2">
         <v>83</v>
@@ -32557,10 +32553,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -32687,10 +32683,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -32819,10 +32815,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -32848,7 +32844,7 @@
         <v>270</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="M226" t="s" s="2">
         <v>272</v>
@@ -32922,7 +32918,7 @@
         <v>83</v>
       </c>
       <c r="AL226" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="AM226" t="s" s="2">
         <v>83</v>
@@ -32951,10 +32947,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -32980,7 +32976,7 @@
         <v>270</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="M227" t="s" s="2">
         <v>282</v>
@@ -33056,7 +33052,7 @@
         <v>83</v>
       </c>
       <c r="AL227" t="s" s="2">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="AM227" t="s" s="2">
         <v>83</v>
@@ -33085,10 +33081,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -33114,10 +33110,10 @@
         <v>494</v>
       </c>
       <c r="L228" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="M228" t="s" s="2">
         <v>765</v>
-      </c>
-      <c r="M228" t="s" s="2">
-        <v>766</v>
       </c>
       <c r="N228" s="2"/>
       <c r="O228" s="2"/>
@@ -33168,7 +33164,7 @@
         <v>83</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>84</v>
@@ -33204,7 +33200,7 @@
         <v>83</v>
       </c>
       <c r="AR228" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="AS228" t="s" s="2">
         <v>83</v>
@@ -33215,13 +33211,13 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
+        <v>878</v>
+      </c>
+      <c r="B229" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="C229" t="s" s="2">
         <v>879</v>
-      </c>
-      <c r="B229" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="C229" t="s" s="2">
-        <v>880</v>
       </c>
       <c r="D229" t="s" s="2">
         <v>83</v>
@@ -33243,13 +33239,13 @@
         <v>83</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -33300,7 +33296,7 @@
         <v>83</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>84</v>
@@ -33333,13 +33329,13 @@
         <v>83</v>
       </c>
       <c r="AQ229" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="AR229" t="s" s="2">
         <v>736</v>
       </c>
-      <c r="AR229" t="s" s="2">
+      <c r="AS229" t="s" s="2">
         <v>737</v>
-      </c>
-      <c r="AS229" t="s" s="2">
-        <v>738</v>
       </c>
       <c r="AT229" t="s" s="2">
         <v>83</v>
@@ -33347,10 +33343,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -33477,10 +33473,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -33609,14 +33605,14 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E232" s="2"/>
       <c r="F232" t="s" s="2">
@@ -33638,10 +33634,10 @@
         <v>121</v>
       </c>
       <c r="L232" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="M232" t="s" s="2">
         <v>743</v>
-      </c>
-      <c r="M232" t="s" s="2">
-        <v>744</v>
       </c>
       <c r="N232" t="s" s="2">
         <v>124</v>
@@ -33696,7 +33692,7 @@
         <v>83</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>84</v>
@@ -33743,10 +33739,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -33772,14 +33768,14 @@
         <v>380</v>
       </c>
       <c r="L233" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="M233" t="s" s="2">
         <v>747</v>
-      </c>
-      <c r="M233" t="s" s="2">
-        <v>748</v>
       </c>
       <c r="N233" s="2"/>
       <c r="O233" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="P233" t="s" s="2">
         <v>83</v>
@@ -33828,7 +33824,7 @@
         <v>83</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>84</v>
@@ -33864,7 +33860,7 @@
         <v>83</v>
       </c>
       <c r="AR233" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="AS233" t="s" s="2">
         <v>83</v>
@@ -33875,10 +33871,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -33904,10 +33900,10 @@
         <v>243</v>
       </c>
       <c r="L234" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="M234" t="s" s="2">
         <v>753</v>
-      </c>
-      <c r="M234" t="s" s="2">
-        <v>754</v>
       </c>
       <c r="N234" s="2"/>
       <c r="O234" s="2"/>
@@ -33938,7 +33934,7 @@
       </c>
       <c r="Y234" s="2"/>
       <c r="Z234" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AA234" t="s" s="2">
         <v>83</v>
@@ -33956,7 +33952,7 @@
         <v>83</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>100</v>
@@ -33971,7 +33967,7 @@
         <v>112</v>
       </c>
       <c r="AK234" t="s" s="2">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="AL234" t="s" s="2">
         <v>83</v>
@@ -33992,10 +33988,10 @@
         <v>83</v>
       </c>
       <c r="AR234" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AS234" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AT234" t="s" s="2">
         <v>83</v>
@@ -34003,10 +33999,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -34133,10 +34129,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -34265,10 +34261,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -34340,7 +34336,7 @@
         <v>83</v>
       </c>
       <c r="AB237" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AC237" s="2"/>
       <c r="AD237" t="s" s="2">
@@ -34397,13 +34393,13 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="D238" t="s" s="2">
         <v>83</v>
@@ -34428,7 +34424,7 @@
         <v>163</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="M238" t="s" s="2">
         <v>413</v>
@@ -34466,7 +34462,7 @@
       </c>
       <c r="Y238" s="2"/>
       <c r="Z238" t="s" s="2">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="AA238" t="s" s="2">
         <v>83</v>
@@ -34531,13 +34527,13 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D239" t="s" s="2">
         <v>83</v>
@@ -34562,7 +34558,7 @@
         <v>163</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="M239" t="s" s="2">
         <v>413</v>
@@ -34600,7 +34596,7 @@
       </c>
       <c r="Y239" s="2"/>
       <c r="Z239" t="s" s="2">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="AA239" t="s" s="2">
         <v>83</v>
@@ -34665,10 +34661,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -34799,10 +34795,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -34828,14 +34824,14 @@
         <v>263</v>
       </c>
       <c r="L241" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="M241" t="s" s="2">
         <v>759</v>
-      </c>
-      <c r="M241" t="s" s="2">
-        <v>760</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="P241" t="s" s="2">
         <v>83</v>
@@ -34884,7 +34880,7 @@
         <v>83</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>84</v>
@@ -34920,10 +34916,10 @@
         <v>83</v>
       </c>
       <c r="AR241" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="AS241" t="s" s="2">
         <v>762</v>
-      </c>
-      <c r="AS241" t="s" s="2">
-        <v>763</v>
       </c>
       <c r="AT241" t="s" s="2">
         <v>83</v>
@@ -34931,10 +34927,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -35061,10 +35057,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -35193,10 +35189,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -35222,7 +35218,7 @@
         <v>270</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="M244" t="s" s="2">
         <v>272</v>
@@ -35293,7 +35289,7 @@
         <v>112</v>
       </c>
       <c r="AK244" t="s" s="2">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="AL244" t="s" s="2">
         <v>83</v>
@@ -35325,10 +35321,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -35354,7 +35350,7 @@
         <v>270</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="M245" t="s" s="2">
         <v>282</v>
@@ -35427,7 +35423,7 @@
         <v>112</v>
       </c>
       <c r="AK245" t="s" s="2">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="AL245" t="s" s="2">
         <v>83</v>
@@ -35459,10 +35455,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -35488,10 +35484,10 @@
         <v>494</v>
       </c>
       <c r="L246" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="M246" t="s" s="2">
         <v>765</v>
-      </c>
-      <c r="M246" t="s" s="2">
-        <v>766</v>
       </c>
       <c r="N246" s="2"/>
       <c r="O246" s="2"/>
@@ -35542,7 +35538,7 @@
         <v>83</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>84</v>
@@ -35578,7 +35574,7 @@
         <v>83</v>
       </c>
       <c r="AR246" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="AS246" t="s" s="2">
         <v>83</v>
@@ -35589,10 +35585,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -35615,19 +35611,19 @@
         <v>83</v>
       </c>
       <c r="K247" t="s" s="2">
+        <v>908</v>
+      </c>
+      <c r="L247" t="s" s="2">
         <v>909</v>
       </c>
-      <c r="L247" t="s" s="2">
+      <c r="M247" t="s" s="2">
         <v>910</v>
       </c>
-      <c r="M247" t="s" s="2">
+      <c r="N247" t="s" s="2">
         <v>911</v>
       </c>
-      <c r="N247" t="s" s="2">
+      <c r="O247" t="s" s="2">
         <v>912</v>
-      </c>
-      <c r="O247" t="s" s="2">
-        <v>913</v>
       </c>
       <c r="P247" t="s" s="2">
         <v>83</v>
@@ -35656,7 +35652,7 @@
       </c>
       <c r="Y247" s="2"/>
       <c r="Z247" t="s" s="2">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="AA247" t="s" s="2">
         <v>83</v>
@@ -35674,7 +35670,7 @@
         <v>83</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>84</v>
@@ -35707,10 +35703,10 @@
         <v>83</v>
       </c>
       <c r="AQ247" t="s" s="2">
+        <v>914</v>
+      </c>
+      <c r="AR247" t="s" s="2">
         <v>915</v>
-      </c>
-      <c r="AR247" t="s" s="2">
-        <v>916</v>
       </c>
       <c r="AS247" t="s" s="2">
         <v>83</v>
